--- a/DEU_WB_timeseries.xlsx
+++ b/DEU_WB_timeseries.xlsx
@@ -14,21 +14,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>Bank capital to assets ratio (%)</t>
+  </si>
+  <si>
+    <t>Bank nonperforming loans (% of gross loans)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government revenue (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
     <t>Interest payments (% of GDP)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Net lending/borrowing (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
     <t>Tax revenue (% of GDP)</t>
   </si>
   <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -389,12 +473,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AH26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -411,496 +495,2455 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:34">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="D2">
+        <v>1.80154538154602</v>
+      </c>
+      <c r="E2">
+        <v>-1.5131310276989</v>
+      </c>
+      <c r="G2">
+        <v>29.6806532498145</v>
+      </c>
+      <c r="H2">
         <v>2.87724595591061</v>
       </c>
-      <c r="C2">
+      <c r="I2">
+        <v>27467.7824174767</v>
+      </c>
+      <c r="J2">
+        <v>23925.8559901991</v>
+      </c>
+      <c r="K2">
+        <v>2.73801195996828</v>
+      </c>
+      <c r="L2">
+        <v>28.9</v>
+      </c>
+      <c r="M2">
+        <v>1.80453169345856</v>
+      </c>
+      <c r="N2">
+        <v>18.860569292751</v>
+      </c>
+      <c r="O2">
+        <v>31.0107716724735</v>
+      </c>
+      <c r="P2">
+        <v>30.0072312012246</v>
+      </c>
+      <c r="Q2">
+        <v>29.5149460477259</v>
+      </c>
+      <c r="R2">
         <v>1.4402683871974</v>
       </c>
-      <c r="D2">
+      <c r="S2">
         <v>6.82682640243238</v>
       </c>
-      <c r="E2">
+      <c r="T2">
+        <v>77.92682926829271</v>
+      </c>
+      <c r="U2">
+        <v>1.35888303317903</v>
+      </c>
+      <c r="V2">
+        <v>-1.16769813021797</v>
+      </c>
+      <c r="W2">
+        <v>1.41133570671082</v>
+      </c>
+      <c r="X2">
+        <v>82211508</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>1.45614349842072</v>
+      </c>
+      <c r="AA2">
+        <v>1.60941886901855</v>
+      </c>
+      <c r="AB2">
         <v>11.6587154757097</v>
       </c>
-      <c r="F2">
+      <c r="AC2">
+        <v>87496869035.2706</v>
+      </c>
+      <c r="AD2">
+        <v>1.49405697641971</v>
+      </c>
+      <c r="AE2">
+        <v>59.1955992975405</v>
+      </c>
+      <c r="AF2">
         <v>7.917</v>
       </c>
+      <c r="AG2">
+        <v>74.965</v>
+      </c>
+      <c r="AH2">
+        <v>1.31480205059052</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:34">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="E3">
+        <v>-0.17042466008937</v>
+      </c>
+      <c r="F3">
+        <v>111.240170458005</v>
+      </c>
+      <c r="G3">
+        <v>30.5604113813066</v>
+      </c>
+      <c r="H3">
         <v>1.63654099437316</v>
       </c>
-      <c r="C3">
+      <c r="I3">
+        <v>28677.1908591132</v>
+      </c>
+      <c r="J3">
+        <v>23878.3641471651</v>
+      </c>
+      <c r="K3">
+        <v>1.46570628997218</v>
+      </c>
+      <c r="L3">
+        <v>29.9</v>
+      </c>
+      <c r="N3">
+        <v>18.7505067113635</v>
+      </c>
+      <c r="O3">
+        <v>30.4174846164707</v>
+      </c>
+      <c r="P3">
+        <v>29.0723424412329</v>
+      </c>
+      <c r="Q3">
+        <v>28.9988749869052</v>
+      </c>
+      <c r="R3">
         <v>1.98385731334472</v>
       </c>
-      <c r="D3">
+      <c r="S3">
         <v>6.45887769999626</v>
       </c>
-      <c r="E3">
+      <c r="T3">
+        <v>78.3292682926829</v>
+      </c>
+      <c r="U3">
+        <v>1.3234383027941</v>
+      </c>
+      <c r="V3">
+        <v>-1.36440859382473</v>
+      </c>
+      <c r="X3">
+        <v>82349925</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
         <v>10.9562611305698</v>
       </c>
-      <c r="F3">
+      <c r="AC3">
+        <v>82131887553.94141</v>
+      </c>
+      <c r="AD3">
+        <v>1.44677088174588</v>
+      </c>
+      <c r="AE3">
+        <v>59.5592863682118</v>
+      </c>
+      <c r="AF3">
         <v>7.773</v>
       </c>
+      <c r="AG3">
+        <v>75.17</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:34">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="D4">
+        <v>1.88874363899231</v>
+      </c>
+      <c r="E4">
+        <v>1.98424702046954</v>
+      </c>
+      <c r="F4">
+        <v>110.165745012493</v>
+      </c>
+      <c r="G4">
+        <v>31.1904504893495</v>
+      </c>
+      <c r="H4">
         <v>-0.228310223930706</v>
       </c>
-      <c r="C4">
+      <c r="I4">
+        <v>29513.6823267102</v>
+      </c>
+      <c r="J4">
+        <v>25486.5942008748</v>
+      </c>
+      <c r="K4">
+        <v>-0.395913755214309</v>
+      </c>
+      <c r="L4">
+        <v>29.8</v>
+      </c>
+      <c r="M4">
+        <v>1.66001808643341</v>
+      </c>
+      <c r="N4">
+        <v>19.0132502158895</v>
+      </c>
+      <c r="O4">
+        <v>30.8239781232009</v>
+      </c>
+      <c r="P4">
+        <v>28.9525313039724</v>
+      </c>
+      <c r="Q4">
+        <v>27.1421182354634</v>
+      </c>
+      <c r="R4">
         <v>1.42080615551526</v>
       </c>
-      <c r="D4">
+      <c r="S4">
         <v>6.23555436229076</v>
       </c>
-      <c r="E4">
+      <c r="T4">
+        <v>78.2292682926829</v>
+      </c>
+      <c r="U4">
+        <v>1.32795812092343</v>
+      </c>
+      <c r="V4">
+        <v>-2.0335888025331</v>
+      </c>
+      <c r="W4">
+        <v>1.09601747989655</v>
+      </c>
+      <c r="X4">
+        <v>82488495</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>1.51094317436218</v>
+      </c>
+      <c r="AA4">
+        <v>1.63438987731934</v>
+      </c>
+      <c r="AB4">
         <v>10.8344127806563</v>
       </c>
-      <c r="F4">
+      <c r="AC4">
+        <v>89142540697.4245</v>
+      </c>
+      <c r="AD4">
+        <v>1.53474790667413</v>
+      </c>
+      <c r="AE4">
+        <v>58.3325687248129</v>
+      </c>
+      <c r="AF4">
         <v>8.481999999999999</v>
       </c>
+      <c r="AG4">
+        <v>75.374</v>
+      </c>
+      <c r="AH4">
+        <v>1.41403138637543</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:34">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="D5">
+        <v>1.87576138973236</v>
+      </c>
+      <c r="E5">
+        <v>1.53250948753762</v>
+      </c>
+      <c r="F5">
+        <v>108.505942047742</v>
+      </c>
+      <c r="G5">
+        <v>31.2678451095809</v>
+      </c>
+      <c r="H5">
         <v>-0.529929010433477</v>
       </c>
-      <c r="C5">
+      <c r="I5">
+        <v>30305.2575678401</v>
+      </c>
+      <c r="J5">
+        <v>30711.1022511331</v>
+      </c>
+      <c r="K5">
+        <v>-0.584983686364041</v>
+      </c>
+      <c r="L5">
+        <v>29.8</v>
+      </c>
+      <c r="M5">
+        <v>1.35740518569946</v>
+      </c>
+      <c r="N5">
+        <v>19.0734600434664</v>
+      </c>
+      <c r="O5">
+        <v>31.1635970921229</v>
+      </c>
+      <c r="P5">
+        <v>29.4980386556647</v>
+      </c>
+      <c r="Q5">
+        <v>27.6466991846698</v>
+      </c>
+      <c r="R5">
         <v>1.03422218628562</v>
       </c>
-      <c r="D5">
+      <c r="S5">
         <v>5.80008792568418</v>
       </c>
-      <c r="E5">
+      <c r="T5">
+        <v>78.3804878048781</v>
+      </c>
+      <c r="U5">
+        <v>1.31692486502826</v>
+      </c>
+      <c r="V5">
+        <v>-1.66578157005726</v>
+      </c>
+      <c r="W5">
+        <v>0.577859222888947</v>
+      </c>
+      <c r="X5">
+        <v>82534176</v>
+      </c>
+      <c r="Y5">
+        <v>0.2</v>
+      </c>
+      <c r="Z5">
+        <v>1.50187790393829</v>
+      </c>
+      <c r="AA5">
+        <v>1.6375846862793</v>
+      </c>
+      <c r="AB5">
         <v>11.0075820796944</v>
       </c>
-      <c r="F5">
+      <c r="AC5">
+        <v>96835206408.4991</v>
+      </c>
+      <c r="AD5">
+        <v>1.35954156351091</v>
+      </c>
+      <c r="AE5">
+        <v>58.9145442942507</v>
+      </c>
+      <c r="AF5">
         <v>9.779</v>
       </c>
+      <c r="AG5">
+        <v>75.577</v>
+      </c>
+      <c r="AH5">
+        <v>1.41355431079865</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:34">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="D6">
+        <v>1.84006547927856</v>
+      </c>
+      <c r="E6">
+        <v>4.53374240243279</v>
+      </c>
+      <c r="F6">
+        <v>105.024726999965</v>
+      </c>
+      <c r="G6">
+        <v>33.9352126434777</v>
+      </c>
+      <c r="H6">
         <v>1.16236825444811</v>
       </c>
-      <c r="C6">
+      <c r="I6">
+        <v>31757.4177276181</v>
+      </c>
+      <c r="J6">
+        <v>34566.7359143735</v>
+      </c>
+      <c r="K6">
+        <v>1.18433271320626</v>
+      </c>
+      <c r="L6">
+        <v>30.2</v>
+      </c>
+      <c r="M6">
+        <v>1.46714746952057</v>
+      </c>
+      <c r="N6">
+        <v>18.5669242577539</v>
+      </c>
+      <c r="O6">
+        <v>29.9861755573387</v>
+      </c>
+      <c r="P6">
+        <v>28.2726860412378</v>
+      </c>
+      <c r="Q6">
+        <v>28.9712783030388</v>
+      </c>
+      <c r="R6">
         <v>1.66573696655992</v>
       </c>
-      <c r="D6">
+      <c r="S6">
         <v>5.75804070710229</v>
       </c>
-      <c r="E6">
+      <c r="T6">
+        <v>78.6804878048781</v>
+      </c>
+      <c r="U6">
+        <v>1.26895739640399</v>
+      </c>
+      <c r="V6">
+        <v>-1.82343090395283</v>
+      </c>
+      <c r="W6">
+        <v>0.638884365558624</v>
+      </c>
+      <c r="X6">
+        <v>82516260</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>1.46957302093506</v>
+      </c>
+      <c r="AA6">
+        <v>1.62020444869995</v>
+      </c>
+      <c r="AB6">
         <v>10.480323064578</v>
       </c>
-      <c r="F6">
+      <c r="AC6">
+        <v>97169968440.54469</v>
+      </c>
+      <c r="AD6">
+        <v>1.17945114546741</v>
+      </c>
+      <c r="AE6">
+        <v>62.9064909465164</v>
+      </c>
+      <c r="AF6">
         <v>10.727</v>
       </c>
+      <c r="AG6">
+        <v>75.779</v>
+      </c>
+      <c r="AH6">
+        <v>1.4960401058197</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:34">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
-      <c r="B7">
+      <c r="D7">
+        <v>1.87544226646423</v>
+      </c>
+      <c r="E7">
+        <v>4.64324145764123</v>
+      </c>
+      <c r="F7">
+        <v>103.75352043032</v>
+      </c>
+      <c r="G7">
+        <v>35.9531497908166</v>
+      </c>
+      <c r="H7">
         <v>0.885697256705441</v>
       </c>
-      <c r="C7">
+      <c r="I7">
+        <v>32313.736788417</v>
+      </c>
+      <c r="J7">
+        <v>35084.4363546269</v>
+      </c>
+      <c r="K7">
+        <v>0.9429946667456049</v>
+      </c>
+      <c r="L7">
+        <v>31.7</v>
+      </c>
+      <c r="M7">
+        <v>1.5005247592926</v>
+      </c>
+      <c r="N7">
+        <v>18.4739713893822</v>
+      </c>
+      <c r="O7">
+        <v>30.0041707693565</v>
+      </c>
+      <c r="P7">
+        <v>28.1351071285758</v>
+      </c>
+      <c r="Q7">
+        <v>30.9999527026155</v>
+      </c>
+      <c r="R7">
         <v>1.54691114751329</v>
       </c>
-      <c r="D7">
+      <c r="S7">
         <v>5.58275175190955</v>
       </c>
-      <c r="E7">
+      <c r="T7">
+        <v>78.9317073170732</v>
+      </c>
+      <c r="U7">
+        <v>1.06562970052135</v>
+      </c>
+      <c r="V7">
+        <v>-2.17873251609186</v>
+      </c>
+      <c r="W7">
+        <v>0.888915359973907</v>
+      </c>
+      <c r="X7">
+        <v>82469422</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>1.51510655879974</v>
+      </c>
+      <c r="AA7">
+        <v>1.65219819545746</v>
+      </c>
+      <c r="AB7">
         <v>10.7118256360423</v>
       </c>
-      <c r="F7">
+      <c r="AC7">
+        <v>101675919831.833</v>
+      </c>
+      <c r="AD7">
+        <v>1.12734868132122</v>
+      </c>
+      <c r="AE7">
+        <v>66.9531024934321</v>
+      </c>
+      <c r="AF7">
         <v>11.193</v>
       </c>
+      <c r="AG7">
+        <v>75.98</v>
+      </c>
+      <c r="AH7">
+        <v>1.48583388328552</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:34">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
-      <c r="B8">
+      <c r="D8">
+        <v>1.79364252090454</v>
+      </c>
+      <c r="E8">
+        <v>5.83661726884206</v>
+      </c>
+      <c r="F8">
+        <v>100.341277234171</v>
+      </c>
+      <c r="G8">
+        <v>38.9694499171537</v>
+      </c>
+      <c r="H8">
         <v>3.85573614635729</v>
       </c>
-      <c r="C8">
+      <c r="I8">
+        <v>34748.7543257238</v>
+      </c>
+      <c r="J8">
+        <v>36980.3349948954</v>
+      </c>
+      <c r="K8">
+        <v>3.9729489119966</v>
+      </c>
+      <c r="L8">
+        <v>31</v>
+      </c>
+      <c r="M8">
+        <v>1.64597606658936</v>
+      </c>
+      <c r="N8">
+        <v>18.0172946772292</v>
+      </c>
+      <c r="O8">
+        <v>28.6974997733062</v>
+      </c>
+      <c r="P8">
+        <v>27.8950448853754</v>
+      </c>
+      <c r="Q8">
+        <v>33.7897435474697</v>
+      </c>
+      <c r="R8">
         <v>1.57742642840562</v>
       </c>
-      <c r="D8">
+      <c r="S8">
         <v>5.63976025956082</v>
       </c>
-      <c r="E8">
+      <c r="T8">
+        <v>79.13170731707319</v>
+      </c>
+      <c r="U8">
+        <v>1.19930295839133</v>
+      </c>
+      <c r="V8">
+        <v>-1.17382057390631</v>
+      </c>
+      <c r="W8">
+        <v>1.02506959438324</v>
+      </c>
+      <c r="X8">
+        <v>82376451</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>1.56890881061554</v>
+      </c>
+      <c r="AA8">
+        <v>1.77008616924286</v>
+      </c>
+      <c r="AB8">
         <v>10.9320825330355</v>
       </c>
-      <c r="F8">
+      <c r="AC8">
+        <v>111637059518.339</v>
+      </c>
+      <c r="AD8">
+        <v>1.07559747593649</v>
+      </c>
+      <c r="AE8">
+        <v>72.75919346462339</v>
+      </c>
+      <c r="AF8">
         <v>10.277</v>
       </c>
+      <c r="AG8">
+        <v>76.179</v>
+      </c>
+      <c r="AH8">
+        <v>1.3652309179306</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:34">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
-      <c r="B9">
+      <c r="D9">
+        <v>1.72651934623718</v>
+      </c>
+      <c r="E9">
+        <v>6.70574096490581</v>
+      </c>
+      <c r="F9">
+        <v>95.4983439670839</v>
+      </c>
+      <c r="G9">
+        <v>40.6368056265783</v>
+      </c>
+      <c r="H9">
         <v>2.89010717888073</v>
       </c>
-      <c r="C9">
+      <c r="I9">
+        <v>36915.3252832162</v>
+      </c>
+      <c r="J9">
+        <v>42350.9217211489</v>
+      </c>
+      <c r="K9">
+        <v>3.02778238969645</v>
+      </c>
+      <c r="L9">
+        <v>31.2</v>
+      </c>
+      <c r="M9">
+        <v>1.63131237030029</v>
+      </c>
+      <c r="N9">
+        <v>17.5553649959484</v>
+      </c>
+      <c r="O9">
+        <v>27.5320782623062</v>
+      </c>
+      <c r="P9">
+        <v>27.6698712149224</v>
+      </c>
+      <c r="Q9">
+        <v>34.2470360551014</v>
+      </c>
+      <c r="R9">
         <v>2.29834400700951</v>
       </c>
-      <c r="D9">
+      <c r="S9">
         <v>5.85290444989899</v>
       </c>
-      <c r="E9">
+      <c r="T9">
+        <v>79.5341463414634</v>
+      </c>
+      <c r="U9">
+        <v>1.17247176491769</v>
+      </c>
+      <c r="V9">
+        <v>-0.16886815460503</v>
+      </c>
+      <c r="W9">
+        <v>0.995823800563812</v>
+      </c>
+      <c r="X9">
+        <v>82266372</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>1.61616551876068</v>
+      </c>
+      <c r="AA9">
+        <v>1.75559067726135</v>
+      </c>
+      <c r="AB9">
         <v>11.4680869476284</v>
       </c>
-      <c r="F9">
+      <c r="AC9">
+        <v>135932292207.152</v>
+      </c>
+      <c r="AD9">
+        <v>1.0983825764745</v>
+      </c>
+      <c r="AE9">
+        <v>74.8838416816798</v>
+      </c>
+      <c r="AF9">
         <v>8.731999999999999</v>
       </c>
+      <c r="AG9">
+        <v>76.378</v>
+      </c>
+      <c r="AH9">
+        <v>1.33647847175598</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:34">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
-      <c r="B10">
+      <c r="D10">
+        <v>1.74589586257935</v>
+      </c>
+      <c r="E10">
+        <v>5.57681458234834</v>
+      </c>
+      <c r="F10">
+        <v>95.38699762132769</v>
+      </c>
+      <c r="G10">
+        <v>40.9425488863489</v>
+      </c>
+      <c r="H10">
         <v>0.910403214153277</v>
       </c>
-      <c r="C10">
+      <c r="I10">
+        <v>38443.5386278958</v>
+      </c>
+      <c r="J10">
+        <v>46386.3295924799</v>
+      </c>
+      <c r="K10">
+        <v>1.10245965834785</v>
+      </c>
+      <c r="L10">
+        <v>30.8</v>
+      </c>
+      <c r="M10">
+        <v>1.51405537128448</v>
+      </c>
+      <c r="N10">
+        <v>17.9510982051837</v>
+      </c>
+      <c r="O10">
+        <v>27.801002440456</v>
+      </c>
+      <c r="P10">
+        <v>27.946850576133</v>
+      </c>
+      <c r="Q10">
+        <v>35.1588613264959</v>
+      </c>
+      <c r="R10">
         <v>2.6283798163722</v>
       </c>
-      <c r="D10">
+      <c r="S10">
         <v>5.83229276192884</v>
       </c>
-      <c r="E10">
+      <c r="T10">
+        <v>79.7365853658537</v>
+      </c>
+      <c r="U10">
+        <v>1.20903400366779</v>
+      </c>
+      <c r="V10">
+        <v>-0.295519137499614</v>
+      </c>
+      <c r="W10">
+        <v>0.943830788135529</v>
+      </c>
+      <c r="X10">
+        <v>82110097</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>1.48888456821442</v>
+      </c>
+      <c r="AA10">
+        <v>1.73402619361877</v>
+      </c>
+      <c r="AB10">
         <v>11.6247953415094</v>
       </c>
-      <c r="F10">
+      <c r="AC10">
+        <v>138564426162.199</v>
+      </c>
+      <c r="AD10">
+        <v>1.03763135561576</v>
+      </c>
+      <c r="AE10">
+        <v>76.1014102128448</v>
+      </c>
+      <c r="AF10">
         <v>7.508</v>
       </c>
+      <c r="AG10">
+        <v>76.575</v>
+      </c>
+      <c r="AH10">
+        <v>1.33677780628204</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:34">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
-      <c r="B11">
+      <c r="D11">
+        <v>1.74621033668518</v>
+      </c>
+      <c r="E11">
+        <v>5.87415966958685</v>
+      </c>
+      <c r="F11">
+        <v>96.82440367634391</v>
+      </c>
+      <c r="G11">
+        <v>35.4417264226192</v>
+      </c>
+      <c r="H11">
         <v>-5.54516454479311</v>
       </c>
-      <c r="C11">
+      <c r="I11">
+        <v>37554.4426993174</v>
+      </c>
+      <c r="J11">
+        <v>42487.2137101496</v>
+      </c>
+      <c r="K11">
+        <v>-5.30552819048091</v>
+      </c>
+      <c r="L11">
+        <v>30.5</v>
+      </c>
+      <c r="M11">
+        <v>1.57510924339294</v>
+      </c>
+      <c r="N11">
+        <v>19.5979349625431</v>
+      </c>
+      <c r="O11">
+        <v>30.434571741213</v>
+      </c>
+      <c r="P11">
+        <v>28.9546549519614</v>
+      </c>
+      <c r="Q11">
+        <v>30.6735421084064</v>
+      </c>
+      <c r="R11">
         <v>0.312739007368444</v>
       </c>
-      <c r="D11">
+      <c r="S11">
         <v>5.2309815712568</v>
       </c>
-      <c r="E11">
+      <c r="T11">
+        <v>79.83658536585369</v>
+      </c>
+      <c r="U11">
+        <v>1.31060407322149</v>
+      </c>
+      <c r="V11">
+        <v>-2.07072913618746</v>
+      </c>
+      <c r="W11">
+        <v>0.859902501106262</v>
+      </c>
+      <c r="X11">
+        <v>81902307</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>1.51645278930664</v>
+      </c>
+      <c r="AA11">
+        <v>1.64867222309113</v>
+      </c>
+      <c r="AB11">
         <v>11.8302757257893</v>
       </c>
-      <c r="F11">
+      <c r="AC11">
+        <v>179040277106.549</v>
+      </c>
+      <c r="AD11">
+        <v>1.72018124150416</v>
+      </c>
+      <c r="AE11">
+        <v>66.11526853102571</v>
+      </c>
+      <c r="AF11">
         <v>7.88</v>
       </c>
+      <c r="AG11">
+        <v>76.771</v>
+      </c>
+      <c r="AH11">
+        <v>1.33496069908142</v>
+      </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:34">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
-      <c r="B12">
+      <c r="D12">
+        <v>1.76642882823944</v>
+      </c>
+      <c r="E12">
+        <v>5.77101102573257</v>
+      </c>
+      <c r="F12">
+        <v>86.74384379563161</v>
+      </c>
+      <c r="G12">
+        <v>39.4832687323685</v>
+      </c>
+      <c r="H12">
         <v>4.14676755040489</v>
       </c>
-      <c r="C12">
+      <c r="I12">
+        <v>39730.4897885271</v>
+      </c>
+      <c r="J12">
+        <v>42409.9356994694</v>
+      </c>
+      <c r="K12">
+        <v>4.30644105826545</v>
+      </c>
+      <c r="L12">
+        <v>30.2</v>
+      </c>
+      <c r="M12">
+        <v>1.51569378376007</v>
+      </c>
+      <c r="N12">
+        <v>19.1768919673096</v>
+      </c>
+      <c r="O12">
+        <v>30.7473070189522</v>
+      </c>
+      <c r="P12">
+        <v>28.009258197442</v>
+      </c>
+      <c r="Q12">
+        <v>34.3793720327515</v>
+      </c>
+      <c r="R12">
         <v>1.1038103778926</v>
       </c>
-      <c r="D12">
+      <c r="S12">
         <v>4.69772541921111</v>
       </c>
-      <c r="E12">
+      <c r="T12">
+        <v>79.98780487804881</v>
+      </c>
+      <c r="U12">
+        <v>1.26682662611137</v>
+      </c>
+      <c r="V12">
+        <v>-3.1995061275353</v>
+      </c>
+      <c r="W12">
+        <v>0.796834468841553</v>
+      </c>
+      <c r="X12">
+        <v>81776930</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>1.57068610191345</v>
+      </c>
+      <c r="AA12">
+        <v>1.63750469684601</v>
+      </c>
+      <c r="AB12">
         <v>11.3009640451672</v>
       </c>
-      <c r="F12">
+      <c r="AC12">
+        <v>215977935889.943</v>
+      </c>
+      <c r="AD12">
+        <v>1.86141152631237</v>
+      </c>
+      <c r="AE12">
+        <v>73.8626407651201</v>
+      </c>
+      <c r="AF12">
         <v>7.043</v>
       </c>
+      <c r="AG12">
+        <v>76.96599999999999</v>
+      </c>
+      <c r="AH12">
+        <v>1.29778325557709</v>
+      </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:34">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
-      <c r="B13">
+      <c r="D13">
+        <v>1.74194991588593</v>
+      </c>
+      <c r="E13">
+        <v>6.25886646333735</v>
+      </c>
+      <c r="F13">
+        <v>83.2221296232272</v>
+      </c>
+      <c r="G13">
+        <v>41.6299889730367</v>
+      </c>
+      <c r="H13">
         <v>3.75796884487347</v>
       </c>
-      <c r="C13">
+      <c r="I13">
+        <v>43398.3443992496</v>
+      </c>
+      <c r="J13">
+        <v>47646.582043143</v>
+      </c>
+      <c r="K13">
+        <v>5.69928311500732</v>
+      </c>
+      <c r="L13">
+        <v>30.6</v>
+      </c>
+      <c r="M13">
+        <v>1.50013899803162</v>
+      </c>
+      <c r="N13">
+        <v>18.6934322242076</v>
+      </c>
+      <c r="O13">
+        <v>28.3049046331442</v>
+      </c>
+      <c r="P13">
+        <v>28.4815544015052</v>
+      </c>
+      <c r="Q13">
+        <v>36.777324487501</v>
+      </c>
+      <c r="R13">
         <v>2.07517283735874</v>
       </c>
-      <c r="D13">
+      <c r="S13">
         <v>5.39044570017936</v>
       </c>
-      <c r="E13">
+      <c r="T13">
+        <v>80.4365853658537</v>
+      </c>
+      <c r="U13">
+        <v>1.20615033635783</v>
+      </c>
+      <c r="V13">
+        <v>-0.370658815565851</v>
+      </c>
+      <c r="W13">
+        <v>0.842218458652496</v>
+      </c>
+      <c r="X13">
+        <v>80274983</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>1.54886770248413</v>
+      </c>
+      <c r="AA13">
+        <v>1.61821925640106</v>
+      </c>
+      <c r="AB13">
         <v>11.7469548476787</v>
       </c>
-      <c r="F13">
+      <c r="AC13">
+        <v>234104084887.41</v>
+      </c>
+      <c r="AD13">
+        <v>1.73236895371289</v>
+      </c>
+      <c r="AE13">
+        <v>78.40731346053769</v>
+      </c>
+      <c r="AF13">
         <v>5.967</v>
       </c>
+      <c r="AG13">
+        <v>77.16</v>
+      </c>
+      <c r="AH13">
+        <v>1.34921073913574</v>
+      </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:34">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
-      <c r="B14">
+      <c r="D14">
+        <v>1.81763017177582</v>
+      </c>
+      <c r="E14">
+        <v>7.19271816687105</v>
+      </c>
+      <c r="F14">
+        <v>82.1589927081325</v>
+      </c>
+      <c r="G14">
+        <v>42.6688163749205</v>
+      </c>
+      <c r="H14">
         <v>0.47429132103845</v>
       </c>
-      <c r="C14">
+      <c r="I14">
+        <v>44229.3941921739</v>
+      </c>
+      <c r="J14">
+        <v>44735.5882319701</v>
+      </c>
+      <c r="K14">
+        <v>0.285850077448487</v>
+      </c>
+      <c r="L14">
+        <v>31.1</v>
+      </c>
+      <c r="M14">
+        <v>1.53097581863403</v>
+      </c>
+      <c r="N14">
+        <v>18.8977924424542</v>
+      </c>
+      <c r="O14">
+        <v>27.933530449439</v>
+      </c>
+      <c r="P14">
+        <v>28.7348859797599</v>
+      </c>
+      <c r="Q14">
+        <v>36.6316714160221</v>
+      </c>
+      <c r="R14">
         <v>2.00848884782953</v>
       </c>
-      <c r="D14">
+      <c r="S14">
         <v>4.93093595996139</v>
       </c>
-      <c r="E14">
+      <c r="T14">
+        <v>80.5390243902439</v>
+      </c>
+      <c r="U14">
+        <v>1.24167747904608</v>
+      </c>
+      <c r="V14">
+        <v>0.0929873802841043</v>
+      </c>
+      <c r="W14">
+        <v>0.775621294975281</v>
+      </c>
+      <c r="X14">
+        <v>80425823</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>1.52908289432526</v>
+      </c>
+      <c r="AA14">
+        <v>1.66923201084137</v>
+      </c>
+      <c r="AB14">
         <v>11.909776530328</v>
       </c>
-      <c r="F14">
+      <c r="AC14">
+        <v>248856490285.757</v>
+      </c>
+      <c r="AD14">
+        <v>1.99203879709291</v>
+      </c>
+      <c r="AE14">
+        <v>79.3004877909427</v>
+      </c>
+      <c r="AF14">
         <v>5.372</v>
       </c>
+      <c r="AG14">
+        <v>77.17</v>
+      </c>
+      <c r="AH14">
+        <v>1.39373803138733</v>
+      </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:34">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
-      <c r="B15">
+      <c r="D15">
+        <v>1.79800081253052</v>
+      </c>
+      <c r="E15">
+        <v>6.72723104677662</v>
+      </c>
+      <c r="F15">
+        <v>80.6622652827767</v>
+      </c>
+      <c r="G15">
+        <v>41.6686546134315</v>
+      </c>
+      <c r="H15">
         <v>0.386224592046474</v>
       </c>
-      <c r="C15">
+      <c r="I15">
+        <v>45889.0173022052</v>
+      </c>
+      <c r="J15">
+        <v>47220.0102098851</v>
+      </c>
+      <c r="K15">
+        <v>0.112643840643003</v>
+      </c>
+      <c r="L15">
+        <v>31.5</v>
+      </c>
+      <c r="M15">
+        <v>1.51041460037231</v>
+      </c>
+      <c r="N15">
+        <v>19.2479981027315</v>
+      </c>
+      <c r="O15">
+        <v>27.9891744091962</v>
+      </c>
+      <c r="P15">
+        <v>28.9184174548701</v>
+      </c>
+      <c r="Q15">
+        <v>35.8957269607433</v>
+      </c>
+      <c r="R15">
         <v>1.50472330251882</v>
       </c>
-      <c r="D15">
+      <c r="S15">
         <v>3.62703855815623</v>
       </c>
-      <c r="E15">
+      <c r="T15">
+        <v>80.490243902439</v>
+      </c>
+      <c r="U15">
+        <v>1.18525790100841</v>
+      </c>
+      <c r="V15">
+        <v>0.204270249155995</v>
+      </c>
+      <c r="W15">
+        <v>0.92798388004303</v>
+      </c>
+      <c r="X15">
+        <v>80645605</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>1.54434037208557</v>
+      </c>
+      <c r="AA15">
+        <v>1.64198386669159</v>
+      </c>
+      <c r="AB15">
         <v>12.0918431405374</v>
       </c>
-      <c r="F15">
+      <c r="AC15">
+        <v>198535165663.607</v>
+      </c>
+      <c r="AD15">
+        <v>1.54979764395872</v>
+      </c>
+      <c r="AE15">
+        <v>77.5643815741748</v>
+      </c>
+      <c r="AF15">
         <v>5.316</v>
       </c>
+      <c r="AG15">
+        <v>77.18000000000001</v>
+      </c>
+      <c r="AH15">
+        <v>1.40613043308258</v>
+      </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:34">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
-      <c r="B16">
+      <c r="D16">
+        <v>1.81229484081268</v>
+      </c>
+      <c r="E16">
+        <v>7.19249005241927</v>
+      </c>
+      <c r="F16">
+        <v>77.77379512724571</v>
+      </c>
+      <c r="G16">
+        <v>41.6838906996921</v>
+      </c>
+      <c r="H16">
         <v>2.16949889758517</v>
       </c>
-      <c r="C16">
+      <c r="I16">
+        <v>47938.7968210418</v>
+      </c>
+      <c r="J16">
+        <v>48971.0824722599</v>
+      </c>
+      <c r="K16">
+        <v>1.74446394150078</v>
+      </c>
+      <c r="L16">
+        <v>30.8</v>
+      </c>
+      <c r="M16">
+        <v>1.6648246049881</v>
+      </c>
+      <c r="N16">
+        <v>19.2101287363869</v>
+      </c>
+      <c r="O16">
+        <v>27.5095890686293</v>
+      </c>
+      <c r="P16">
+        <v>28.9186210500575</v>
+      </c>
+      <c r="Q16">
+        <v>35.1464405712237</v>
+      </c>
+      <c r="R16">
         <v>0.906794000434214</v>
       </c>
-      <c r="D16">
+      <c r="S16">
         <v>3.27943712189847</v>
       </c>
-      <c r="E16">
+      <c r="T16">
+        <v>81.090243902439</v>
+      </c>
+      <c r="U16">
+        <v>1.14994199690514</v>
+      </c>
+      <c r="V16">
+        <v>0.684115142521196</v>
+      </c>
+      <c r="W16">
+        <v>0.925186455249786</v>
+      </c>
+      <c r="X16">
+        <v>80982500</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>1.69703912734985</v>
+      </c>
+      <c r="AA16">
+        <v>1.85020470619202</v>
+      </c>
+      <c r="AB16">
         <v>12.0473875859666</v>
       </c>
-      <c r="F16">
+      <c r="AC16">
+        <v>193484758847.919</v>
+      </c>
+      <c r="AD16">
+        <v>1.48007833557917</v>
+      </c>
+      <c r="AE16">
+        <v>76.83033127091591</v>
+      </c>
+      <c r="AF16">
         <v>4.979</v>
       </c>
+      <c r="AG16">
+        <v>77.19</v>
+      </c>
+      <c r="AH16">
+        <v>1.43629622459412</v>
+      </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:34">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
-      <c r="B17">
+      <c r="D17">
+        <v>1.7758332490921</v>
+      </c>
+      <c r="E17">
+        <v>8.10033539639848</v>
+      </c>
+      <c r="F17">
+        <v>76.61575356894009</v>
+      </c>
+      <c r="G17">
+        <v>42.6044431481211</v>
+      </c>
+      <c r="H17">
         <v>1.65271978656361</v>
       </c>
-      <c r="C17">
+      <c r="I17">
+        <v>48558.4432970969</v>
+      </c>
+      <c r="J17">
+        <v>41911.0109851054</v>
+      </c>
+      <c r="K17">
+        <v>0.776507671684243</v>
+      </c>
+      <c r="L17">
+        <v>31.7</v>
+      </c>
+      <c r="M17">
+        <v>1.65639758110046</v>
+      </c>
+      <c r="N17">
+        <v>19.3122356715765</v>
+      </c>
+      <c r="O17">
+        <v>27.4487709234683</v>
+      </c>
+      <c r="P17">
+        <v>28.8956621781472</v>
+      </c>
+      <c r="Q17">
+        <v>35.1869136162559</v>
+      </c>
+      <c r="R17">
         <v>0.514426137125455</v>
       </c>
-      <c r="D17">
+      <c r="S17">
         <v>2.84235743052022</v>
       </c>
-      <c r="E17">
+      <c r="T17">
+        <v>80.6414634146341</v>
+      </c>
+      <c r="U17">
+        <v>1.13733842666332</v>
+      </c>
+      <c r="V17">
+        <v>0.679370635036378</v>
+      </c>
+      <c r="W17">
+        <v>0.687514960765839</v>
+      </c>
+      <c r="X17">
+        <v>81686611</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>1.71191465854645</v>
+      </c>
+      <c r="AA17">
+        <v>1.75914001464844</v>
+      </c>
+      <c r="AB17">
         <v>11.9939072804758</v>
       </c>
-      <c r="F17">
+      <c r="AC17">
+        <v>173730930555.425</v>
+      </c>
+      <c r="AD17">
+        <v>1.53866263784816</v>
+      </c>
+      <c r="AE17">
+        <v>77.791356764377</v>
+      </c>
+      <c r="AF17">
         <v>4.612</v>
       </c>
+      <c r="AG17">
+        <v>77.2</v>
+      </c>
+      <c r="AH17">
+        <v>1.42213714122772</v>
+      </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:34">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
-      <c r="B18">
+      <c r="D18">
+        <v>1.78129398822784</v>
+      </c>
+      <c r="E18">
+        <v>8.89985353214632</v>
+      </c>
+      <c r="F18">
+        <v>75.9672852311091</v>
+      </c>
+      <c r="G18">
+        <v>41.6238177033957</v>
+      </c>
+      <c r="H18">
         <v>2.29471066413561</v>
       </c>
-      <c r="C18">
+      <c r="I18">
+        <v>51569.9016841199</v>
+      </c>
+      <c r="J18">
+        <v>42961.0356905775</v>
+      </c>
+      <c r="K18">
+        <v>1.47229261688244</v>
+      </c>
+      <c r="L18">
+        <v>31.4</v>
+      </c>
+      <c r="M18">
+        <v>1.66018795967102</v>
+      </c>
+      <c r="N18">
+        <v>19.5190716214398</v>
+      </c>
+      <c r="O18">
+        <v>27.3671431834324</v>
+      </c>
+      <c r="P18">
+        <v>28.8136203071859</v>
+      </c>
+      <c r="Q18">
+        <v>34.3607698108013</v>
+      </c>
+      <c r="R18">
         <v>0.491747008445213</v>
       </c>
-      <c r="D18">
+      <c r="S18">
         <v>2.38097415752432</v>
       </c>
-      <c r="E18">
+      <c r="T18">
+        <v>80.990243902439</v>
+      </c>
+      <c r="U18">
+        <v>1.15123037317289</v>
+      </c>
+      <c r="V18">
+        <v>0.736708060736333</v>
+      </c>
+      <c r="W18">
+        <v>0.667541146278381</v>
+      </c>
+      <c r="X18">
+        <v>82348669</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>1.8065539598465</v>
+      </c>
+      <c r="AA18">
+        <v>1.58330154418945</v>
+      </c>
+      <c r="AB18">
         <v>11.8311322201051</v>
       </c>
-      <c r="F18">
+      <c r="AC18">
+        <v>184031339953.397</v>
+      </c>
+      <c r="AD18">
+        <v>1.62420238995537</v>
+      </c>
+      <c r="AE18">
+        <v>75.9845875141969</v>
+      </c>
+      <c r="AF18">
         <v>4.104</v>
       </c>
+      <c r="AG18">
+        <v>77.224</v>
+      </c>
+      <c r="AH18">
+        <v>1.3646674156189</v>
+      </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:34">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
-      <c r="B19">
+      <c r="D19">
+        <v>1.79697561264038</v>
+      </c>
+      <c r="E19">
+        <v>8.08358573755333</v>
+      </c>
+      <c r="F19">
+        <v>76.10475186949699</v>
+      </c>
+      <c r="G19">
+        <v>42.3259814296135</v>
+      </c>
+      <c r="H19">
         <v>2.71602454639843</v>
       </c>
-      <c r="C19">
+      <c r="I19">
+        <v>54110.2536648812</v>
+      </c>
+      <c r="J19">
+        <v>45526.5999576533</v>
+      </c>
+      <c r="K19">
+        <v>2.33286596055396</v>
+      </c>
+      <c r="L19">
+        <v>31.3</v>
+      </c>
+      <c r="M19">
+        <v>1.61311173439026</v>
+      </c>
+      <c r="N19">
+        <v>19.4595495195295</v>
+      </c>
+      <c r="O19">
+        <v>27.5391986454965</v>
+      </c>
+      <c r="P19">
+        <v>28.9994026015352</v>
+      </c>
+      <c r="Q19">
+        <v>35.24065551723</v>
+      </c>
+      <c r="R19">
         <v>1.50949485109622</v>
       </c>
-      <c r="D19">
+      <c r="S19">
         <v>2.01022280214659</v>
       </c>
-      <c r="E19">
+      <c r="T19">
+        <v>80.9926829268293</v>
+      </c>
+      <c r="U19">
+        <v>1.15340372066259</v>
+      </c>
+      <c r="V19">
+        <v>0.636664655325102</v>
+      </c>
+      <c r="W19">
+        <v>0.574381291866302</v>
+      </c>
+      <c r="X19">
+        <v>82657002</v>
+      </c>
+      <c r="Y19">
+        <v>0.2</v>
+      </c>
+      <c r="Z19">
+        <v>1.77526342868805</v>
+      </c>
+      <c r="AA19">
+        <v>1.5740704536438</v>
+      </c>
+      <c r="AB19">
         <v>11.9806911209777</v>
       </c>
-      <c r="F19">
+      <c r="AC19">
+        <v>199983070123.869</v>
+      </c>
+      <c r="AD19">
+        <v>1.62554687781984</v>
+      </c>
+      <c r="AE19">
+        <v>77.5666369468435</v>
+      </c>
+      <c r="AF19">
         <v>3.781</v>
       </c>
+      <c r="AG19">
+        <v>77.261</v>
+      </c>
+      <c r="AH19">
+        <v>1.43248081207275</v>
+      </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:34">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
-      <c r="B20">
+      <c r="D20">
+        <v>1.89839863777161</v>
+      </c>
+      <c r="E20">
+        <v>8.444743690797971</v>
+      </c>
+      <c r="F20">
+        <v>76.6835998636018</v>
+      </c>
+      <c r="G20">
+        <v>42.6073917339186</v>
+      </c>
+      <c r="H20">
         <v>1.11644310902427</v>
       </c>
-      <c r="C20">
+      <c r="I20">
+        <v>56273.0405627017</v>
+      </c>
+      <c r="J20">
+        <v>48874.8595028454</v>
+      </c>
+      <c r="K20">
+        <v>0.8130173634392009</v>
+      </c>
+      <c r="L20">
+        <v>31.9</v>
+      </c>
+      <c r="M20">
+        <v>1.52356374263763</v>
+      </c>
+      <c r="N20">
+        <v>19.5022339579089</v>
+      </c>
+      <c r="O20">
+        <v>27.3876244852279</v>
+      </c>
+      <c r="P20">
+        <v>29.3106352717618</v>
+      </c>
+      <c r="Q20">
+        <v>36.6202679583694</v>
+      </c>
+      <c r="R20">
         <v>1.73216879766948</v>
       </c>
-      <c r="D20">
+      <c r="S20">
         <v>1.83695947132345</v>
       </c>
-      <c r="E20">
+      <c r="T20">
+        <v>80.89268292682929</v>
+      </c>
+      <c r="U20">
+        <v>1.17054854477113</v>
+      </c>
+      <c r="V20">
+        <v>1.11187859393261</v>
+      </c>
+      <c r="W20">
+        <v>0.577865242958069</v>
+      </c>
+      <c r="X20">
+        <v>82905782</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>1.75632679462433</v>
+      </c>
+      <c r="AA20">
+        <v>1.59137535095215</v>
+      </c>
+      <c r="AB20">
         <v>11.9612489179949</v>
       </c>
-      <c r="F20">
+      <c r="AC20">
+        <v>198027061675.403</v>
+      </c>
+      <c r="AD20">
+        <v>1.45449826289867</v>
+      </c>
+      <c r="AE20">
+        <v>79.227659692288</v>
+      </c>
+      <c r="AF20">
         <v>3.384</v>
       </c>
+      <c r="AG20">
+        <v>77.312</v>
+      </c>
+      <c r="AH20">
+        <v>1.44311714172363</v>
+      </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:34">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
-      <c r="B21">
+      <c r="D21">
+        <v>1.86510336399078</v>
+      </c>
+      <c r="E21">
+        <v>7.88005874480123</v>
+      </c>
+      <c r="F21">
+        <v>78.01863146698049</v>
+      </c>
+      <c r="G21">
+        <v>42.3863044855837</v>
+      </c>
+      <c r="H21">
         <v>0.987893350164853</v>
       </c>
-      <c r="C21">
+      <c r="I21">
+        <v>59270.7276496985</v>
+      </c>
+      <c r="J21">
+        <v>47623.8656074829</v>
+      </c>
+      <c r="K21">
+        <v>0.7604021954111601</v>
+      </c>
+      <c r="L21">
+        <v>31.8</v>
+      </c>
+      <c r="M21">
+        <v>1.49534583091736</v>
+      </c>
+      <c r="N21">
+        <v>19.9030235821301</v>
+      </c>
+      <c r="O21">
+        <v>27.899362920382</v>
+      </c>
+      <c r="P21">
+        <v>29.5696034943195</v>
+      </c>
+      <c r="Q21">
+        <v>36.747442628887</v>
+      </c>
+      <c r="R21">
         <v>1.44565976888253</v>
       </c>
-      <c r="D21">
+      <c r="S21">
         <v>1.54206664104667</v>
       </c>
-      <c r="E21">
+      <c r="T21">
+        <v>81.2926829268293</v>
+      </c>
+      <c r="U21">
+        <v>1.26184145004044</v>
+      </c>
+      <c r="V21">
+        <v>0.767069886389354</v>
+      </c>
+      <c r="W21">
+        <v>0.548539876937866</v>
+      </c>
+      <c r="X21">
+        <v>83092962</v>
+      </c>
+      <c r="Y21">
+        <v>0.2</v>
+      </c>
+      <c r="Z21">
+        <v>1.71493887901306</v>
+      </c>
+      <c r="AA21">
+        <v>1.5813193321228</v>
+      </c>
+      <c r="AB21">
         <v>11.9105599058525</v>
       </c>
-      <c r="F21">
+      <c r="AC21">
+        <v>224027961016.415</v>
+      </c>
+      <c r="AD21">
+        <v>1.68680367954395</v>
+      </c>
+      <c r="AE21">
+        <v>79.13374711447059</v>
+      </c>
+      <c r="AF21">
         <v>3.163</v>
       </c>
+      <c r="AG21">
+        <v>77.376</v>
+      </c>
+      <c r="AH21">
+        <v>1.35402822494507</v>
+      </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:34">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
-      <c r="B22">
+      <c r="D22">
+        <v>1.82534158229828</v>
+      </c>
+      <c r="E22">
+        <v>6.34985102790796</v>
+      </c>
+      <c r="F22">
+        <v>83.83610368678291</v>
+      </c>
+      <c r="G22">
+        <v>39.1691838521344</v>
+      </c>
+      <c r="H22">
         <v>-4.09513751682526</v>
       </c>
-      <c r="C22">
+      <c r="I22">
+        <v>58685.872699771</v>
+      </c>
+      <c r="J22">
+        <v>47379.765194548</v>
+      </c>
+      <c r="K22">
+        <v>-4.17345323463887</v>
+      </c>
+      <c r="L22">
+        <v>32.4</v>
+      </c>
+      <c r="M22">
+        <v>1.31368815898895</v>
+      </c>
+      <c r="N22">
+        <v>21.7313211310231</v>
+      </c>
+      <c r="O22">
+        <v>32.1608467019556</v>
+      </c>
+      <c r="P22">
+        <v>29.5153669099785</v>
+      </c>
+      <c r="Q22">
+        <v>33.824073376198</v>
+      </c>
+      <c r="R22">
         <v>0.144877925813963</v>
       </c>
-      <c r="D22">
+      <c r="S22">
         <v>0.975458502452167</v>
       </c>
-      <c r="E22">
+      <c r="T22">
+        <v>81.04146341463419</v>
+      </c>
+      <c r="U22">
+        <v>1.37427175481016</v>
+      </c>
+      <c r="V22">
+        <v>-3.65712745171932</v>
+      </c>
+      <c r="W22">
+        <v>0.645049154758453</v>
+      </c>
+      <c r="X22">
+        <v>83160871</v>
+      </c>
+      <c r="Y22">
+        <v>0.2</v>
+      </c>
+      <c r="Z22">
+        <v>1.57793474197388</v>
+      </c>
+      <c r="AA22">
+        <v>1.52012777328491</v>
+      </c>
+      <c r="AB22">
         <v>11.1683895617488</v>
       </c>
-      <c r="F22">
+      <c r="AC22">
+        <v>268408603348.679</v>
+      </c>
+      <c r="AD22">
+        <v>2.2194147879826</v>
+      </c>
+      <c r="AE22">
+        <v>72.9932572283324</v>
+      </c>
+      <c r="AF22">
         <v>3.881</v>
       </c>
+      <c r="AG22">
+        <v>77.453</v>
+      </c>
+      <c r="AH22">
+        <v>1.37390911579132</v>
+      </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:34">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
-      <c r="B23">
+      <c r="D23">
+        <v>1.7829247713089</v>
+      </c>
+      <c r="E23">
+        <v>6.93113737824586</v>
+      </c>
+      <c r="F23">
+        <v>82.8360977679616</v>
+      </c>
+      <c r="G23">
+        <v>42.6575836538409</v>
+      </c>
+      <c r="H23">
         <v>3.6699998840452</v>
       </c>
-      <c r="C23">
+      <c r="I23">
+        <v>62530.7653199239</v>
+      </c>
+      <c r="J23">
+        <v>52265.6541620571</v>
+      </c>
+      <c r="K23">
+        <v>3.62612870918142</v>
+      </c>
+      <c r="M23">
+        <v>1.28911292552948</v>
+      </c>
+      <c r="N23">
+        <v>21.6742192217514</v>
+      </c>
+      <c r="O23">
+        <v>32.720769435816</v>
+      </c>
+      <c r="P23">
+        <v>29.2673114898571</v>
+      </c>
+      <c r="Q23">
+        <v>37.4990343972191</v>
+      </c>
+      <c r="R23">
         <v>3.0666666666667</v>
       </c>
-      <c r="D23">
+      <c r="S23">
         <v>0.884646781372042</v>
       </c>
-      <c r="E23">
+      <c r="T23">
+        <v>80.790243902439</v>
+      </c>
+      <c r="U23">
+        <v>1.32102724294738</v>
+      </c>
+      <c r="V23">
+        <v>-3.52298134618628</v>
+      </c>
+      <c r="W23">
+        <v>0.725788176059723</v>
+      </c>
+      <c r="X23">
+        <v>83196078</v>
+      </c>
+      <c r="Z23">
+        <v>1.62516117095947</v>
+      </c>
+      <c r="AA23">
+        <v>1.5718047618866</v>
+      </c>
+      <c r="AB23">
         <v>11.4951883061423</v>
       </c>
-      <c r="F23">
+      <c r="AC23">
+        <v>295736219413.597</v>
+      </c>
+      <c r="AD23">
+        <v>1.99690469909917</v>
+      </c>
+      <c r="AE23">
+        <v>80.15661805105999</v>
+      </c>
+      <c r="AF23">
         <v>3.594</v>
       </c>
+      <c r="AG23">
+        <v>77.544</v>
+      </c>
+      <c r="AH23">
+        <v>1.41956698894501</v>
+      </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:34">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
+        <v>7.00177428428283</v>
+      </c>
+      <c r="C24">
+        <v>1.23497612551348</v>
+      </c>
+      <c r="D24">
+        <v>1.81836342811584</v>
+      </c>
+      <c r="E24">
+        <v>3.88506689580802</v>
+      </c>
+      <c r="F24">
+        <v>81.80798462258301</v>
+      </c>
+      <c r="G24">
+        <v>45.7805177232318</v>
+      </c>
+      <c r="H24">
         <v>1.36973104612758</v>
       </c>
-      <c r="C24">
+      <c r="I24">
+        <v>67589.8399055414</v>
+      </c>
+      <c r="J24">
+        <v>49686.1154582583</v>
+      </c>
+      <c r="K24">
+        <v>0.641609114499019</v>
+      </c>
+      <c r="M24">
+        <v>1.28929960727692</v>
+      </c>
+      <c r="N24">
+        <v>21.5213273138839</v>
+      </c>
+      <c r="O24">
+        <v>31.4551133705123</v>
+      </c>
+      <c r="P24">
+        <v>28.7571607420615</v>
+      </c>
+      <c r="Q24">
+        <v>43.2836096462941</v>
+      </c>
+      <c r="R24">
         <v>6.87257438551096</v>
       </c>
-      <c r="D24">
+      <c r="S24">
         <v>1.36489215944835</v>
       </c>
-      <c r="E24">
+      <c r="T24">
+        <v>80.60804878048781</v>
+      </c>
+      <c r="U24">
+        <v>1.37713842050552</v>
+      </c>
+      <c r="V24">
+        <v>-2.69223668070362</v>
+      </c>
+      <c r="W24">
+        <v>0.628491878509521</v>
+      </c>
+      <c r="X24">
+        <v>83797985</v>
+      </c>
+      <c r="Z24">
+        <v>1.52229499816895</v>
+      </c>
+      <c r="AA24">
+        <v>1.53199517726898</v>
+      </c>
+      <c r="AB24">
         <v>11.3053353060941</v>
       </c>
-      <c r="F24">
+      <c r="AC24">
+        <v>293913690186.797</v>
+      </c>
+      <c r="AD24">
+        <v>1.76247470845575</v>
+      </c>
+      <c r="AE24">
+        <v>89.06412736952591</v>
+      </c>
+      <c r="AF24">
         <v>3.12</v>
       </c>
+      <c r="AG24">
+        <v>77.648</v>
+      </c>
+      <c r="AH24">
+        <v>1.41448700428009</v>
+      </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:34">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
+        <v>7.2943063747054</v>
+      </c>
+      <c r="C25">
+        <v>1.53513253215758</v>
+      </c>
+      <c r="D25">
+        <v>1.66416621208191</v>
+      </c>
+      <c r="E25">
+        <v>5.55668585897884</v>
+      </c>
+      <c r="F25">
+        <v>77.8765992521891</v>
+      </c>
+      <c r="G25">
+        <v>43.4023485563427</v>
+      </c>
+      <c r="H25">
         <v>-0.266438401180253</v>
       </c>
-      <c r="C25">
+      <c r="I25">
+        <v>68692.894466622</v>
+      </c>
+      <c r="J25">
+        <v>53940.4073447462</v>
+      </c>
+      <c r="K25">
+        <v>-0.38998869126668</v>
+      </c>
+      <c r="M25">
+        <v>1.18541669845581</v>
+      </c>
+      <c r="N25">
+        <v>21.2287274073897</v>
+      </c>
+      <c r="P25">
+        <v>28.5623633692107</v>
+      </c>
+      <c r="Q25">
+        <v>39.3967578932279</v>
+      </c>
+      <c r="R25">
         <v>5.94643667725828</v>
       </c>
-      <c r="E25">
+      <c r="T25">
+        <v>80.54146341463419</v>
+      </c>
+      <c r="U25">
+        <v>1.51965192096975</v>
+      </c>
+      <c r="V25">
+        <v>-2.04816571298874</v>
+      </c>
+      <c r="W25">
+        <v>0.586989283561707</v>
+      </c>
+      <c r="X25">
+        <v>83901923</v>
+      </c>
+      <c r="Z25">
+        <v>1.45697498321533</v>
+      </c>
+      <c r="AA25">
+        <v>1.55120778083801</v>
+      </c>
+      <c r="AB25">
         <v>10.7213866755862</v>
       </c>
-      <c r="F25">
+      <c r="AC25">
+        <v>322700066274.527</v>
+      </c>
+      <c r="AD25">
+        <v>1.86701248940273</v>
+      </c>
+      <c r="AE25">
+        <v>82.7991064495705</v>
+      </c>
+      <c r="AF25">
         <v>3.068</v>
       </c>
+      <c r="AG25">
+        <v>77.765</v>
+      </c>
+      <c r="AH25">
+        <v>1.46138572692871</v>
+      </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:34">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26">
+      <c r="E26">
+        <v>5.66583562733218</v>
+      </c>
+      <c r="G26">
+        <v>42.1002680442064</v>
+      </c>
+      <c r="H26">
         <v>-0.238526858256165</v>
       </c>
-      <c r="C26">
+      <c r="I26">
+        <v>72300.1205050011</v>
+      </c>
+      <c r="J26">
+        <v>55800.2194549412</v>
+      </c>
+      <c r="K26">
+        <v>0.228526174174277</v>
+      </c>
+      <c r="Q26">
+        <v>38.2444033577531</v>
+      </c>
+      <c r="R26">
         <v>2.25649814338757</v>
       </c>
-      <c r="F26">
+      <c r="X26">
+        <v>83510950</v>
+      </c>
+      <c r="AC26">
+        <v>377935574356.242</v>
+      </c>
+      <c r="AD26">
+        <v>2.19310945333811</v>
+      </c>
+      <c r="AE26">
+        <v>80.3446714019595</v>
+      </c>
+      <c r="AF26">
         <v>3.406</v>
+      </c>
+      <c r="AG26">
+        <v>77.895</v>
       </c>
     </row>
   </sheetData>
